--- a/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élie aide maman dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Élie sent ses joues brûlantes. Il baisse les yeux. Élie dit : je suis gêné. Maman dit : une erreur, ce n'est pas toi. L'erreur, on peut la dire. Élie dit : j'ai versé la farine. Maman tend un torchon. Élie dit : je veux réparer. Il essuie la table. Maman aide un peu. Plus tard, au salon, Élie range des livres. Un livre tombe. Encore une erreur. Les joues d'Élie chauffent. Il dit : je suis gêné. Puis il ramasse le livre. Il le pose. Il a su réparer. Maman dit : merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. L'erreur n'est pas Élie.</t>
+          <t>Élie aide maman dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Élie sent ses joues brûlantes. Il baisse les yeux. Je suis gêné. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé la farine. Maman tend un torchon. Je veux réparer. Il essuie la table. Maman aide un peu. Plus tard, au salon, Élie range des livres. Un livre tombe. Encore une erreur. Les joues d'Élie chauffent. Je suis gêné. Puis il ramasse le livre. Il le pose. Il a su réparer. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. L'erreur n'est pas Élie.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,20 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Élie aide maman dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Élie sent ses joues brûlantes. Il baisse les yeux.
+enfant-f|Je suis gêné.
+maman|Une erreur, ce n'est pas toi. L'erreur, on peut la dire.
+enfant-f|J'ai versé la farine. Maman tend un torchon.
+enfant-f|Je veux réparer. Il essuie la table. Maman aide un peu. Plus tard, au salon, Élie range des livres.
+narrateur|Un livre tombe. Encore une erreur. Les joues d'Élie chauffent.
+narrateur|Je suis gêné.
+narrateur|Puis il ramasse le livre. Il le pose. Il a su réparer.
+maman|Merci d'avoir dit. Être gêné, on le dit.
+narrateur|Puis on peut réparer. L'erreur n'est pas Élie.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1499,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Élie a fait une erreur. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Élie a nommé : gêné. L'erreur n'est pas Élie. Il a pu réparer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1835,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La table est propre. Le livre est rangé. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2002,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2042,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1319,6 +1324,7 @@
 narrateur|Puis on peut réparer. L'erreur n'est pas Élie.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1506,6 +1512,7 @@
           <t>narrateur|Élie a fait une erreur. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1684,7 @@
           <t>narrateur|Élie a nommé : gêné. L'erreur n'est pas Élie. Il a pu réparer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1840,6 +1848,7 @@
           <t>narrateur|La table est propre. Le livre est rangé. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2007,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Élie est gêné, puis il répare</t>
+          <t>Victorino est gêné, puis il répare</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino verse de la farine, puis un livre tombe. Deux fois, il dit qu'il est gêné. Deux fois, il répare.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élie aide maman dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Élie sent ses joues brûlantes. Il baisse les yeux. Je suis gêné. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé la farine. Maman tend un torchon. Je veux réparer. Il essuie la table. Maman aide un peu. Plus tard, au salon, Élie range des livres. Un livre tombe. Encore une erreur. Les joues d'Élie chauffent. Je suis gêné. Puis il ramasse le livre. Il le pose. Il a su réparer. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. L'erreur n'est pas Élie.</t>
+          <t>Le livre de recettes reste ouvert sur la table. Une page montre un gâteau tout simple. Une empreinte de farine a déjà marqué le coin. Ça sent un peu la cannelle. La cuisine est tiède, comme après un four. Un torchon à pois attend près de l'évier. Dehors, un oiseau crie, puis plus. Victorino, tu m'aides pour la farine ? Oui, maman. Je porte le bol. Tout doux, jusqu'ici. En ce moment, Victorino aide dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Un nuage blanc s'assoit sur le bois, et sur la page. Victorino sent ses joues brûlantes. Il baisse les yeux. Je suis gêné. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé la farine. Merci d'avoir dit. Voici le torchon. Je veux réparer. Il essuie la table. Maman aide un peu, au coin de la page. Bravo. Tu as dit. Tu répares. Plus tard, au salon, le tapis est doux. Une lampe fait un rond jaune sur les livres. Un marque-page rouge dépasse d'un gros livre. On range les livres, maintenant ? Oui. Je les mets sur l'étagère. Un livre tombe. Encore une erreur. Les joues de Victorino chauffent. Je suis gêné. Tu peux le dire encore. Puis il ramasse le livre. Il le pose. Il a su réparer. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. L'erreur n'est pas moi. Oui. Bravo, Victorino. C'est du bon travail. Le livre de recettes reste propre, dans la cuisine. Le livre du salon est rangé. Tes joues sont moins chaudes ? Oui, maman. On dit. Puis on répare.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Élie aide maman dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Élie sent ses joues brûlantes. Il baisse les yeux.
-enfant-f|Je suis gêné.
-maman|Une erreur, ce n'est pas toi. L'erreur, on peut la dire.
-enfant-f|J'ai versé la farine. Maman tend un torchon.
-enfant-f|Je veux réparer. Il essuie la table. Maman aide un peu. Plus tard, au salon, Élie range des livres.
-narrateur|Un livre tombe. Encore une erreur. Les joues d'Élie chauffent.
-narrateur|Je suis gêné.
-narrateur|Puis il ramasse le livre. Il le pose. Il a su réparer.
-maman|Merci d'avoir dit. Être gêné, on le dit.
-narrateur|Puis on peut réparer. L'erreur n'est pas Élie.</t>
+          <t>narrateur|Le livre de recettes reste ouvert sur la table.
+narrateur|Une page montre un gâteau tout simple.
+narrateur|Une empreinte de farine a déjà marqué le coin.
+narrateur|Ça sent un peu la cannelle.
+narrateur|La cuisine est tiède, comme après un four.
+narrateur|Un torchon à pois attend près de l'évier.
+narrateur|Dehors, un oiseau crie, puis plus.
+maman|Victorino, tu m'aides pour la farine ?
+enfant-m|Oui, maman.
+enfant-m|Je porte le bol.
+maman|Tout doux, jusqu'ici.
+narrateur|En ce moment, Victorino aide dans la cuisine.
+narrateur|Il porte un bol de farine.
+narrateur|Le bol penche.
+narrateur|La farine glisse sur la table.
+narrateur|Un nuage blanc s'assoit sur le bois, et sur la page.
+narrateur|Victorino sent ses joues brûlantes.
+narrateur|Il baisse les yeux.
+enfant-m|Je suis gêné.
+maman|Une erreur, ce n'est pas toi.
+maman|L'erreur, on peut la dire.
+enfant-m|J'ai versé la farine.
+maman|Merci d'avoir dit.
+maman|Voici le torchon.
+enfant-m|Je veux réparer.
+narrateur|Il essuie la table.
+narrateur|Maman aide un peu, au coin de la page.
+maman|Bravo.
+maman|Tu as dit.
+maman|Tu répares.
+narrateur|Plus tard, au salon, le tapis est doux.
+narrateur|Une lampe fait un rond jaune sur les livres.
+narrateur|Un marque-page rouge dépasse d'un gros livre.
+maman|On range les livres, maintenant ?
+enfant-m|Oui.
+enfant-m|Je les mets sur l'étagère.
+narrateur|Un livre tombe.
+narrateur|Encore une erreur.
+narrateur|Les joues de Victorino chauffent.
+enfant-m|Je suis gêné.
+maman|Tu peux le dire encore.
+narrateur|Puis il ramasse le livre.
+narrateur|Il le pose.
+narrateur|Il a su réparer.
+maman|Merci d'avoir dit.
+maman|Être gêné, on le dit.
+maman|Puis on peut réparer.
+enfant-m|L'erreur n'est pas moi.
+maman|Oui.
+maman|Bravo, Victorino.
+maman|C'est du bon travail.
+narrateur|Le livre de recettes reste propre, dans la cuisine.
+narrateur|Le livre du salon est rangé.
+maman|Tes joues sont moins chaudes ?
+enfant-m|Oui, maman.
+maman|On dit.
+maman|Puis on répare.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1349,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Élie a fait une erreur. Que fait-il ?</t>
+          <t>Victorino a fait une erreur. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1509,7 +1568,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Élie a fait une erreur. Que fait-il ?</t>
+          <t>narrateur|Victorino a fait une erreur.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1537,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Élie a nommé : gêné. L'erreur n'est pas Élie. Il a pu réparer.</t>
+          <t>Victorino a nommé : gêné. L'erreur n'est pas Victorino. Il a pu réparer. Je suis gêné. J'ai dit. J'ai réparé. Oui. Deux fois, tu as dit. Deux fois, tu as réparé. Bravo. C'est du bon travail. Le torchon repose près de l'évier. Le livre repose sur l'étagère. Être gêné, on le dit. Puis on répare. L'erreur n'est pas moi. Le marque-page rouge est encore là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1681,7 +1741,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Élie a nommé : gêné. L'erreur n'est pas Élie. Il a pu réparer.</t>
+          <t>narrateur|Victorino a nommé : gêné.
+narrateur|L'erreur n'est pas Victorino.
+narrateur|Il a pu réparer.
+enfant-m|Je suis gêné.
+enfant-m|J'ai dit.
+enfant-m|J'ai réparé.
+maman|Oui.
+maman|Deux fois, tu as dit.
+maman|Deux fois, tu as réparé.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Le torchon repose près de l'évier.
+narrateur|Le livre repose sur l'étagère.
+maman|Être gêné, on le dit.
+maman|Puis on répare.
+enfant-m|L'erreur n'est pas moi.
+narrateur|Le marque-page rouge est encore là.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1709,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La table est propre. Le livre est rangé. Maman sourit.</t>
+          <t>La table est propre. Le livre est rangé. On reste un peu au salon ? Oui. Près de la lampe. Tu as dit l'erreur. Tu as réparé. Bravo. J'étais gêné. Deux fois. Et deux fois, tu as su réparer. Le rond jaune de la lampe reste sur le tapis. On lit une page, tout doux ? Oui. Une petite page. Les pages sentent le papier.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1845,7 +1921,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La table est propre. Le livre est rangé. Maman sourit.</t>
+          <t>narrateur|La table est propre.
+narrateur|Le livre est rangé.
+maman|On reste un peu au salon ?
+enfant-m|Oui.
+enfant-m|Près de la lampe.
+maman|Tu as dit l'erreur.
+maman|Tu as réparé.
+maman|Bravo.
+enfant-m|J'étais gêné.
+enfant-m|Deux fois.
+maman|Et deux fois, tu as su réparer.
+narrateur|Le rond jaune de la lampe reste sur le tapis.
+maman|On lit une page, tout doux ?
+enfant-m|Oui.
+enfant-m|Une petite page.
+narrateur|Les pages sentent le papier.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1873,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais gêné. J'ai dit. J'ai réparé. Bravo, Victorino. Tu as fait du bon travail. La table est propre. Le livre est rangé. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2013,7 +2104,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais gêné.
+enfant-m|J'ai dit.
+enfant-m|J'ai réparé.
+maman|Bravo, Victorino.
+maman|Tu as fait du bon travail.
+narrateur|La table est propre.
+narrateur|Le livre est rangé.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2035,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le livre de recettes reste ouvert sur la table. Une page montre un gâteau tout simple. Une empreinte de farine a déjà marqué le coin. Ça sent un peu la cannelle. La cuisine est tiède, comme après un four. Un torchon à pois attend près de l'évier. Dehors, un oiseau crie, puis plus. Victorino, tu m'aides pour la farine ? Oui, maman. Je porte le bol. Tout doux, jusqu'ici. En ce moment, Victorino aide dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Un nuage blanc s'assoit sur le bois, et sur la page. Victorino sent ses joues brûlantes. Il baisse les yeux. Je suis gêné. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé la farine. Merci d'avoir dit. Voici le torchon. Je veux réparer. Il essuie la table. Maman aide un peu, au coin de la page. Bravo. Tu as dit. Tu répares. Plus tard, au salon, le tapis est doux. Une lampe fait un rond jaune sur les livres. Un marque-page rouge dépasse d'un gros livre. On range les livres, maintenant ? Oui. Je les mets sur l'étagère. Un livre tombe. Encore une erreur. Les joues de Victorino chauffent. Je suis gêné. Tu peux le dire encore. Puis il ramasse le livre. Il le pose. Il a su réparer. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. L'erreur n'est pas moi. Oui. Bravo, Victorino. C'est du bon travail. Le livre de recettes reste propre, dans la cuisine. Le livre du salon est rangé. Tes joues sont moins chaudes ? Oui, maman. On dit. Puis on répare.</t>
+          <t>Le livre de recettes reste ouvert sur la table. Une page montre un gâteau tout simple. Une empreinte de farine a déjà marqué le coin. Ça sent un peu la cannelle. La cuisine est tiède, comme après un four. Un torchon à pois attend près de l'évier. Dehors, un oiseau crie, puis plus. Victorino, tu m'aides pour la farine ? Oui, maman. Je porte le bol. Tout doux, jusqu'ici. En ce moment, Victorino aide dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Un nuage blanc s'assoit sur le bois, et sur la page. Victorino sent ses joues brûlantes. Il baisse les yeux. Je suis gêné. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé la farine. Merci d'avoir dit. Voici le torchon. Je veux réparer. Il essuie la table. Maman aide un peu, au coin de la page. Bravo. Tu as dit. Tu répares. Plus tard, au salon, le tapis est doux. Une lampe fait un rond jaune sur les livres. Un marque-page rouge dépasse d'un gros livre. On range les livres, maintenant ? Oui. Je les mets sur l'étagère. Un livre tombe. Encore une erreur. Les joues de Victorino chauffent. Je suis gêné. Tu peux le dire encore. Puis il ramasse le livre. Il le pose. Il a su réparer. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. L'erreur n'est pas moi. Oui. Bravo, Victorino. Le livre de recettes reste propre, dans la cuisine. Le livre du salon est rangé. Tes joues sont moins chaudes ? Oui, maman. On dit. Puis on répare.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élie aide maman dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Élie sent ses joues brûlantes. Il baisse les yeux. Élie dit : je suis &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;. Maman dit : une erreur, ce n'est pas toi. L'erreur, on peut la dire. Élie dit : j'ai versé la farine. Maman tend un torchon. Élie dit : je veux réparer. Il essuie la table. Maman aide un peu. Plus tard, au salon, Élie range des livres. Un livre tombe. Encore une erreur. Les joues d'Élie chauffent. Il dit : je suis gêné. Puis il ramasse le livre. Il le pose. Il a su réparer. Maman dit : merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. L'erreur n'est pas Élie.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le livre de recettes reste ouvert sur la table. Une page montre un gâteau tout simple. Une empreinte de farine a déjà marqué le coin. Ça sent un peu la cannelle. La cuisine est tiède, comme après un four. Un torchon à pois attend près de l'évier. Dehors, un oiseau crie, puis plus. Victorino, tu m'aides pour la farine ? Oui, maman. Je porte le bol. Tout doux, jusqu'ici. En ce moment, Victorino aide dans la cuisine. Il porte un bol de farine. Le bol penche. La farine glisse sur la table. Un nuage blanc s'assoit sur le bois, et sur la page. Victorino sent ses joues brûlantes. Il baisse les yeux. Je suis gêné. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé la farine. Merci d'avoir dit. Voici le torchon. Je veux réparer. Il essuie la table. Maman aide un peu, au coin de la page. Bravo. Tu as dit. Tu répares. Plus tard, au salon, le tapis est doux. Une lampe fait un rond jaune sur les livres. Un marque-page rouge dépasse d'un gros livre. On range les livres, maintenant ? Oui. Je les mets sur l'étagère. Un livre tombe. Encore une erreur. Les joues de Victorino chauffent. Je suis gêné. Tu peux le dire encore. Puis il ramasse le livre. Il le pose. Il a su réparer. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. L'erreur n'est pas moi. Oui. Bravo, Victorino. Le livre de recettes reste propre, dans la cuisine. Le livre du salon est rangé. Tes joues sont moins chaudes ? Oui, maman. On dit. Puis on répare.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1374,7 +1374,6 @@
 enfant-m|L'erreur n'est pas moi.
 maman|Oui.
 maman|Bravo, Victorino.
-maman|C'est du bon travail.
 narrateur|Le livre de recettes reste propre, dans la cuisine.
 narrateur|Le livre du salon est rangé.
 maman|Tes joues sont moins chaudes ?
@@ -1383,7 +1382,6 @@
 maman|Puis on répare.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1413,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élie a fait une &lt;emphasis level="moderate"&gt;erreur&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a fait une erreur. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1572,7 +1570,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1597,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a nommé : gêné. L'erreur n'est pas Victorino. Il a pu réparer. Je suis gêné. J'ai dit. J'ai réparé. Oui. Deux fois, tu as dit. Deux fois, tu as réparé. Bravo. C'est du bon travail. Le torchon repose près de l'évier. Le livre repose sur l'étagère. Être gêné, on le dit. Puis on répare. L'erreur n'est pas moi. Le marque-page rouge est encore là.</t>
+          <t>Victorino a nommé : gêné. L'erreur n'est pas Victorino. Il a pu réparer. Je suis gêné. J'ai dit. J'ai réparé. Oui. Deux fois, tu as dit. Deux fois, tu as réparé. Bravo. Le torchon repose près de l'évier. Le livre repose sur l'étagère. Être gêné, on le dit. Puis on répare. L'erreur n'est pas moi. Le marque-page rouge est encore là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élie a nommé : &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;. L'erreur n'est pas Élie. Il a pu réparer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a nommé : gêné. L'erreur n'est pas Victorino. Il a pu réparer. Je suis gêné. J'ai dit. J'ai réparé. Oui. Deux fois, tu as dit. Deux fois, tu as réparé. Bravo. Le torchon repose près de l'évier. Le livre repose sur l'étagère. Être gêné, on le dit. Puis on répare. L'erreur n'est pas moi. Le marque-page rouge est encore là.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,7 +1748,6 @@
 maman|Deux fois, tu as dit.
 maman|Deux fois, tu as réparé.
 maman|Bravo.
-maman|C'est du bon travail.
 narrateur|Le torchon repose près de l'évier.
 narrateur|Le livre repose sur l'étagère.
 maman|Être gêné, on le dit.
@@ -1760,7 +1756,6 @@
 narrateur|Le marque-page rouge est encore là.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1785,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La table est propre. Le livre est rangé. Maman sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La table est propre. Le livre est rangé. On reste un peu au salon ? Oui. Près de la lampe. Tu as dit l'erreur. Tu as réparé. Bravo. J'étais gêné. Deux fois. Et deux fois, tu as su réparer. Le rond jaune de la lampe reste sur le tapis. On lit une page, tout doux ? Oui. Une petite page. Les pages sentent le papier.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,7 +1934,6 @@
 narrateur|Les pages sentent le papier.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1964,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais gêné. J'ai dit. J'ai réparé. Bravo, Victorino. Tu as fait du bon travail. La table est propre. Le livre est rangé. L'histoire est finie.</t>
+          <t>J'étais gêné. J'ai dit. J'ai réparé. Bravo, Victorino. La table est propre. Le livre est rangé.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais gêné. J'ai dit. J'ai réparé. Bravo, Victorino. La table est propre. Le livre est rangé.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,13 +2102,10 @@
 enfant-m|J'ai dit.
 enfant-m|J'ai réparé.
 maman|Bravo, Victorino.
-maman|Tu as fait du bon travail.
 narrateur|La table est propre.
-narrateur|Le livre est rangé.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le livre est rangé.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Élie, maman</t>
+          <t>Victorino, maman</t>
         </is>
       </c>
     </row>
